--- a/event_registration_forms/037_vendor_set_up_time_selection--event_registration_forms.xlsx
+++ b/event_registration_forms/037_vendor_set_up_time_selection--event_registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -669,8 +669,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -698,12 +698,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'morning'}</t>
+          <t>morning</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Morning'}</t>
+          <t>Morning</t>
         </is>
       </c>
     </row>
@@ -715,12 +715,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'afternoon'}</t>
+          <t>afternoon</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Afternoon'}</t>
+          <t>Afternoon</t>
         </is>
       </c>
     </row>
@@ -732,12 +732,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'evening'}</t>
+          <t>evening</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Evening'}</t>
+          <t>Evening</t>
         </is>
       </c>
     </row>
@@ -749,12 +749,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -766,12 +766,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'electrical'}</t>
+          <t>electrical</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Electrical'}</t>
+          <t>Electrical</t>
         </is>
       </c>
     </row>
@@ -783,12 +783,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'internet'}</t>
+          <t>internet</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Internet'}</t>
+          <t>Internet</t>
         </is>
       </c>
     </row>
@@ -800,12 +800,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'water'}</t>
+          <t>water</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Water'}</t>
+          <t>Water</t>
         </is>
       </c>
     </row>
@@ -817,12 +817,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'parking'}</t>
+          <t>parking</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Parking'}</t>
+          <t>Parking</t>
         </is>
       </c>
     </row>
